--- a/experiment_results/wedos_grid/rtt_bursts_S4_atk1pct_wu300000_stage1a_rep1.xlsx
+++ b/experiment_results/wedos_grid/rtt_bursts_S4_atk1pct_wu300000_stage1a_rep1.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
